--- a/medical_consent_forms/021_medical_informed_consent_form--medical_consent_forms.xlsx
+++ b/medical_consent_forms/021_medical_informed_consent_form--medical_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>me</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>me</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mi</t>
+          <t>mn</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mn</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mo</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>mt</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ne</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nv</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>NH</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nh</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NJ</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nj</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NM</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ny</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>nd</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>ND</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nd</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>oh</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>pa</t>
+          <t>ri</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RI</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ri</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RI</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ut</t>
+          <t>vt</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>VT</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>vt</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>va</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>wa</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>WI</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>wi</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>wv</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WV</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
@@ -2078,27 +2078,10 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>wy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>medical_license_state_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
